--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408003</v>
+        <v>123407902</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>79879</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483086</v>
+        <v>483057</v>
       </c>
       <c r="R2" t="n">
-        <v>6843218</v>
+        <v>6843247</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408031</v>
+        <v>123408003</v>
       </c>
       <c r="B3" t="n">
         <v>78769</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483105</v>
+        <v>483086</v>
       </c>
       <c r="R3" t="n">
-        <v>6843208</v>
+        <v>6843218</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123407902</v>
+        <v>123408031</v>
       </c>
       <c r="B4" t="n">
-        <v>79879</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483057</v>
+        <v>483105</v>
       </c>
       <c r="R4" t="n">
-        <v>6843247</v>
+        <v>6843208</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123407902</v>
+        <v>123408003</v>
       </c>
       <c r="B2" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483057</v>
+        <v>483086</v>
       </c>
       <c r="R2" t="n">
-        <v>6843247</v>
+        <v>6843218</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408003</v>
+        <v>123408031</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483086</v>
+        <v>483105</v>
       </c>
       <c r="R3" t="n">
-        <v>6843218</v>
+        <v>6843208</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408031</v>
+        <v>123407902</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>79881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483105</v>
+        <v>483057</v>
       </c>
       <c r="R4" t="n">
-        <v>6843208</v>
+        <v>6843247</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123408003</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>123408031</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>123407902</v>
       </c>
       <c r="B4" t="n">
-        <v>79881</v>
+        <v>79882</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408003</v>
+        <v>123408031</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483086</v>
+        <v>483105</v>
       </c>
       <c r="R2" t="n">
-        <v>6843218</v>
+        <v>6843208</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408031</v>
+        <v>123408003</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483105</v>
+        <v>483086</v>
       </c>
       <c r="R3" t="n">
-        <v>6843208</v>
+        <v>6843218</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +887,7 @@
         <v>123407902</v>
       </c>
       <c r="B4" t="n">
-        <v>79882</v>
+        <v>79885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408031</v>
+        <v>123408003</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483105</v>
+        <v>483086</v>
       </c>
       <c r="R2" t="n">
-        <v>6843208</v>
+        <v>6843218</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408003</v>
+        <v>123408031</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483086</v>
+        <v>483105</v>
       </c>
       <c r="R3" t="n">
-        <v>6843218</v>
+        <v>6843208</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +887,7 @@
         <v>123407902</v>
       </c>
       <c r="B4" t="n">
-        <v>79885</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408003</v>
+        <v>123407902</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>79896</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483086</v>
+        <v>483057</v>
       </c>
       <c r="R2" t="n">
-        <v>6843218</v>
+        <v>6843247</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408031</v>
+        <v>123408003</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483105</v>
+        <v>483086</v>
       </c>
       <c r="R3" t="n">
-        <v>6843208</v>
+        <v>6843218</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123407902</v>
+        <v>123408031</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483057</v>
+        <v>483105</v>
       </c>
       <c r="R4" t="n">
-        <v>6843247</v>
+        <v>6843208</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123407902</v>
+        <v>123408031</v>
       </c>
       <c r="B2" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483057</v>
+        <v>483105</v>
       </c>
       <c r="R2" t="n">
-        <v>6843247</v>
+        <v>6843208</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +785,7 @@
         <v>123408003</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408031</v>
+        <v>123407902</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>79898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483105</v>
+        <v>483057</v>
       </c>
       <c r="R4" t="n">
-        <v>6843208</v>
+        <v>6843247</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408031</v>
+        <v>123407902</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483105</v>
+        <v>483057</v>
       </c>
       <c r="R2" t="n">
-        <v>6843208</v>
+        <v>6843247</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123407902</v>
+        <v>123408031</v>
       </c>
       <c r="B4" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483057</v>
+        <v>483105</v>
       </c>
       <c r="R4" t="n">
-        <v>6843247</v>
+        <v>6843208</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123407902</v>
+        <v>123408031</v>
       </c>
       <c r="B2" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483057</v>
+        <v>483105</v>
       </c>
       <c r="R2" t="n">
-        <v>6843247</v>
+        <v>6843208</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408003</v>
+        <v>123407902</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483086</v>
+        <v>483057</v>
       </c>
       <c r="R3" t="n">
-        <v>6843218</v>
+        <v>6843247</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408031</v>
+        <v>123408003</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483105</v>
+        <v>483086</v>
       </c>
       <c r="R4" t="n">
-        <v>6843208</v>
+        <v>6843218</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123407902</v>
+        <v>123408003</v>
       </c>
       <c r="B3" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483057</v>
+        <v>483086</v>
       </c>
       <c r="R3" t="n">
-        <v>6843247</v>
+        <v>6843218</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408003</v>
+        <v>123407902</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483086</v>
+        <v>483057</v>
       </c>
       <c r="R4" t="n">
-        <v>6843218</v>
+        <v>6843247</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408031</v>
+        <v>123408003</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483105</v>
+        <v>483086</v>
       </c>
       <c r="R2" t="n">
-        <v>6843208</v>
+        <v>6843218</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408003</v>
+        <v>123408031</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483086</v>
+        <v>483105</v>
       </c>
       <c r="R3" t="n">
-        <v>6843218</v>
+        <v>6843208</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>123408003</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -780,16 +775,11 @@
         <v>123408031</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -884,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123407902</v>
+        <v>123408047</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +909,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483057</v>
+        <v>483103</v>
       </c>
       <c r="R4" t="n">
-        <v>6843247</v>
+        <v>6843198</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,15 +964,112 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123407902</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483057</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6843247</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>lennart karlsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>lennart karlsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26527-2023 artfynd.xlsx
+++ b/artfynd/A 26527-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408047</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,8 +1090,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123407902</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>